--- a/excel_routes/route_MED_ATZ_threats.xlsx
+++ b/excel_routes/route_MED_ATZ_threats.xlsx
@@ -1,55 +1,127 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CODERED\LAB\market_insights\outputs\run_generated_311225_at_20.48\reports\excel_routes\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C381F7F3-141F-4FB8-9B98-0309E8E40BA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="THREAT_ALERT" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="THREAT_ALERT" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="18">
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>Air Cairo Flight</t>
+  </si>
+  <si>
+    <t>Market Threat Airline</t>
+  </si>
+  <si>
+    <t>OAL Fare Threat</t>
+  </si>
+  <si>
+    <t>Our Fare</t>
+  </si>
+  <si>
+    <t>Fare Dif</t>
+  </si>
+  <si>
+    <t>OAL Baggage</t>
+  </si>
+  <si>
+    <t>Our Baggage</t>
+  </si>
+  <si>
+    <t>Bag Allowance Dif</t>
+  </si>
+  <si>
+    <t>IMPACT</t>
+  </si>
+  <si>
+    <t>Currency</t>
+  </si>
+  <si>
+    <t>06-JAN-26</t>
+  </si>
+  <si>
+    <t>SM-488</t>
+  </si>
+  <si>
+    <t>EgyptAir MS-694</t>
+  </si>
+  <si>
+    <t>LOW THREAT</t>
+  </si>
+  <si>
+    <t>SAR</t>
+  </si>
+  <si>
+    <t>EgyptAir MS-696</t>
+  </si>
+  <si>
+    <t>EgyptAir MS-640</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="4">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="003498DB"/>
-        <bgColor rgb="003498DB"/>
+        <fgColor rgb="FF3498DB"/>
+        <bgColor rgb="FF3498DB"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D4EDDA"/>
-        <bgColor rgb="00D4EDDA"/>
+        <fgColor rgb="FFD4EDDA"/>
+        <bgColor rgb="FFD4EDDA"/>
       </patternFill>
     </fill>
   </fills>
@@ -62,99 +134,49 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="4">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -442,217 +464,161 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:K4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
-    <col width="17" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
-    <col width="19" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
+    <col min="1" max="1" width="11" customWidth="1"/>
+    <col min="2" max="2" width="18" customWidth="1"/>
+    <col min="3" max="3" width="23" customWidth="1"/>
+    <col min="4" max="4" width="17" customWidth="1"/>
+    <col min="5" max="6" width="10" customWidth="1"/>
+    <col min="7" max="7" width="153.44140625" customWidth="1"/>
+    <col min="8" max="8" width="13" customWidth="1"/>
+    <col min="9" max="9" width="19" customWidth="1"/>
+    <col min="10" max="10" width="12" customWidth="1"/>
+    <col min="11" max="11" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Air Cairo Flight</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Market Threat Airline</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>OAL Fare Threat</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Our Fare</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Fare Dif</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>OAL Baggage</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Our Baggage</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Bag Allowance Dif</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>IMPACT</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Currency</t>
-        </is>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>06-JAN-26</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>SM-488</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-694</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="n">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" s="2">
         <v>666</v>
       </c>
-      <c r="E2" s="2" t="n">
+      <c r="E2" s="2">
         <v>680</v>
       </c>
-      <c r="F2" s="2" t="n">
+      <c r="F2" s="2">
         <v>-14</v>
       </c>
-      <c r="G2" s="2" t="n">
+      <c r="G2" s="2">
         <v>46</v>
       </c>
-      <c r="H2" s="2" t="n">
+      <c r="H2" s="2">
         <v>30</v>
       </c>
-      <c r="I2" s="2" t="n">
+      <c r="I2" s="2">
         <v>-16</v>
       </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
+      <c r="J2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>15</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>06-JAN-26</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>SM-488</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-696</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="n">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" s="2">
         <v>666</v>
       </c>
-      <c r="E3" s="2" t="n">
+      <c r="E3" s="2">
         <v>680</v>
       </c>
-      <c r="F3" s="2" t="n">
+      <c r="F3" s="2">
         <v>-14</v>
       </c>
-      <c r="G3" s="2" t="n">
+      <c r="G3" s="2">
         <v>46</v>
       </c>
-      <c r="H3" s="2" t="n">
+      <c r="H3" s="2">
         <v>30</v>
       </c>
-      <c r="I3" s="2" t="n">
+      <c r="I3" s="2">
         <v>-16</v>
       </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
+      <c r="J3" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>15</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>06-JAN-26</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>SM-488</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-640</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="n">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" s="2">
         <v>666</v>
       </c>
-      <c r="E4" s="2" t="n">
+      <c r="E4" s="2">
         <v>680</v>
       </c>
-      <c r="F4" s="2" t="n">
+      <c r="F4" s="2">
         <v>-14</v>
       </c>
-      <c r="G4" s="2" t="n">
+      <c r="G4" s="2">
         <v>46</v>
       </c>
-      <c r="H4" s="2" t="n">
+      <c r="H4" s="2">
         <v>30</v>
       </c>
-      <c r="I4" s="2" t="n">
+      <c r="I4" s="2">
         <v>-16</v>
       </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
+      <c r="J4" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/excel_routes/route_MED_ATZ_threats.xlsx
+++ b/excel_routes/route_MED_ATZ_threats.xlsx
@@ -1,127 +1,67 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
-  <workbookPr codeName="ThisWorkbook"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CODERED\LAB\market_insights\outputs\run_generated_311225_at_20.48\reports\excel_routes\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C381F7F3-141F-4FB8-9B98-0309E8E40BA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="THREAT_ALERT" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="THREAT_ALERT" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
-  <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="18">
-  <si>
-    <t>Date</t>
-  </si>
-  <si>
-    <t>Air Cairo Flight</t>
-  </si>
-  <si>
-    <t>Market Threat Airline</t>
-  </si>
-  <si>
-    <t>OAL Fare Threat</t>
-  </si>
-  <si>
-    <t>Our Fare</t>
-  </si>
-  <si>
-    <t>Fare Dif</t>
-  </si>
-  <si>
-    <t>OAL Baggage</t>
-  </si>
-  <si>
-    <t>Our Baggage</t>
-  </si>
-  <si>
-    <t>Bag Allowance Dif</t>
-  </si>
-  <si>
-    <t>IMPACT</t>
-  </si>
-  <si>
-    <t>Currency</t>
-  </si>
-  <si>
-    <t>06-JAN-26</t>
-  </si>
-  <si>
-    <t>SM-488</t>
-  </si>
-  <si>
-    <t>EgyptAir MS-694</t>
-  </si>
-  <si>
-    <t>LOW THREAT</t>
-  </si>
-  <si>
-    <t>SAR</t>
-  </si>
-  <si>
-    <t>EgyptAir MS-696</t>
-  </si>
-  <si>
-    <t>EgyptAir MS-640</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="3">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
+      <b val="1"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF3498DB"/>
-        <bgColor rgb="FF3498DB"/>
+        <fgColor rgb="003498DB"/>
+        <bgColor rgb="003498DB"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD4EDDA"/>
-        <bgColor rgb="FFD4EDDA"/>
+        <fgColor rgb="00D4EDDA"/>
+        <bgColor rgb="00D4EDDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8D7DA"/>
+        <bgColor rgb="00F8D7DA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF3CD"/>
+        <bgColor rgb="00FFF3CD"/>
       </patternFill>
     </fill>
   </fills>
@@ -134,49 +74,105 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+  <cellXfs count="6">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -464,161 +460,1297 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:K4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="11" customWidth="1"/>
-    <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="3" width="23" customWidth="1"/>
-    <col min="4" max="4" width="17" customWidth="1"/>
-    <col min="5" max="6" width="10" customWidth="1"/>
-    <col min="7" max="7" width="153.44140625" customWidth="1"/>
-    <col min="8" max="8" width="13" customWidth="1"/>
-    <col min="9" max="9" width="19" customWidth="1"/>
-    <col min="10" max="10" width="12" customWidth="1"/>
-    <col min="11" max="11" width="10" customWidth="1"/>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="19" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Air Cairo Flight</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Market Threat Airline</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>OAL Fare Threat</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Our Fare</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Fare Dif</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>OAL Baggage</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Our Baggage</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Bag Allowance Dif</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>IMPACT</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>06-JAN-26</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>SM-488</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-694</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>666</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>680</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>-14</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>06-JAN-26</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>SM-488</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-696</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>666</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>680</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>-14</v>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I3" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>06-JAN-26</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>SM-488</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-640</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>666</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>680</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>-14</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I4" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>14-FEB-26</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>SM-488</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-696</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>496</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>-4</v>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I5" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>16-FEB-26</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>SM-964</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-676</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>441</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>1691</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>-1250</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>16-FEB-26</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>SM-964</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-694</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>441</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>1691</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>-1250</v>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I7" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>16-FEB-26</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>SM-964</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-696</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>441</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>1691</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>-1250</v>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>16-FEB-26</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>SM-964</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-678</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>498</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>1691</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>-1193</v>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H9" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I9" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>16-FEB-26</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>SM-964</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-640</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>504</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>1691</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>-1187</v>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I10" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>16-FEB-26</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>SM-964</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-381</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>578</v>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>1691</v>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>-1113</v>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H11" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I11" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>16-FEB-26</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>SM-964</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-319</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>578</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>1691</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>-1113</v>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H12" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I12" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>16-FEB-26</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>SM-964</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-391</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>578</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>1691</v>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>-1113</v>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H13" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I13" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>21-FEB-26</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>SM-488</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-771</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>389</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>836</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>-447</v>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H14" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I14" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>21-FEB-26</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>SM-488</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-793</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>559</v>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>836</v>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>-277</v>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H15" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I15" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D2" s="2">
-        <v>666</v>
-      </c>
-      <c r="E2" s="2">
-        <v>680</v>
-      </c>
-      <c r="F2" s="2">
-        <v>-14</v>
-      </c>
-      <c r="G2" s="2">
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>22-FEB-26</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>SM-972</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-775</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>389</v>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>1691</v>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>-1302</v>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H16" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I16" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>22-FEB-26</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>SM-972</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-771</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>449</v>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>1691</v>
+      </c>
+      <c r="F17" s="2" t="n">
+        <v>-1242</v>
+      </c>
+      <c r="G17" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H17" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I17" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>22-FEB-26</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>SM-972</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-319</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>971</v>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>1691</v>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>-720</v>
+      </c>
+      <c r="G18" s="2" t="n">
         <v>46</v>
       </c>
-      <c r="H2" s="2">
-        <v>30</v>
-      </c>
-      <c r="I2" s="2">
+      <c r="H18" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I18" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J2" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" s="2">
-        <v>666</v>
-      </c>
-      <c r="E3" s="2">
-        <v>680</v>
-      </c>
-      <c r="F3" s="2">
-        <v>-14</v>
-      </c>
-      <c r="G3" s="2">
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>22-FEB-26</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>SM-972</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-576</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="n">
+        <v>989</v>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>1691</v>
+      </c>
+      <c r="F19" s="2" t="n">
+        <v>-702</v>
+      </c>
+      <c r="G19" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H19" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>22-FEB-26</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>SM-972</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-391</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>1260</v>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>1691</v>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>-431</v>
+      </c>
+      <c r="G20" s="2" t="n">
         <v>46</v>
       </c>
-      <c r="H3" s="2">
-        <v>30</v>
-      </c>
-      <c r="I3" s="2">
+      <c r="H20" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I20" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J3" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D4" s="2">
-        <v>666</v>
-      </c>
-      <c r="E4" s="2">
-        <v>680</v>
-      </c>
-      <c r="F4" s="2">
-        <v>-14</v>
-      </c>
-      <c r="G4" s="2">
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>22-FEB-26</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>SM-972</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-640</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>1396</v>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>1691</v>
+      </c>
+      <c r="F21" s="2" t="n">
+        <v>-295</v>
+      </c>
+      <c r="G21" s="2" t="n">
         <v>46</v>
       </c>
-      <c r="H4" s="2">
-        <v>30</v>
-      </c>
-      <c r="I4" s="2">
+      <c r="H21" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I21" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J4" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>15</v>
+      <c r="J21" s="5" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>22-FEB-26</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>SM-972</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-678</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>1618</v>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>1691</v>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>-73</v>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H22" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I22" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>22-FEB-26</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>SM-972</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-381</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="n">
+        <v>1643</v>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>1691</v>
+      </c>
+      <c r="F23" s="2" t="n">
+        <v>-48</v>
+      </c>
+      <c r="G23" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H23" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I23" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>23-FEB-26</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>SM-964</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-381</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="n">
+        <v>1260</v>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>1691</v>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v>-431</v>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H24" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I24" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>23-FEB-26</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>SM-964</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-319</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="n">
+        <v>1260</v>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>1691</v>
+      </c>
+      <c r="F25" s="2" t="n">
+        <v>-431</v>
+      </c>
+      <c r="G25" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H25" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I25" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J25" s="4" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>23-FEB-26</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>SM-964</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-640</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="n">
+        <v>1561</v>
+      </c>
+      <c r="E26" s="2" t="n">
+        <v>1691</v>
+      </c>
+      <c r="F26" s="2" t="n">
+        <v>-130</v>
+      </c>
+      <c r="G26" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H26" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I26" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>23-FEB-26</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>SM-964</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-391</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="n">
+        <v>1643</v>
+      </c>
+      <c r="E27" s="2" t="n">
+        <v>1691</v>
+      </c>
+      <c r="F27" s="2" t="n">
+        <v>-48</v>
+      </c>
+      <c r="G27" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H27" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I27" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>23-FEB-26</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>SM-964</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-696</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="n">
+        <v>1726</v>
+      </c>
+      <c r="E28" s="2" t="n">
+        <v>1691</v>
+      </c>
+      <c r="F28" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="G28" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H28" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I28" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/excel_routes/route_MED_ATZ_threats.xlsx
+++ b/excel_routes/route_MED_ATZ_threats.xlsx
@@ -33,7 +33,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -50,6 +50,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00D4EDDA"/>
         <bgColor rgb="00D4EDDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF3CD"/>
+        <bgColor rgb="00FFF3CD"/>
       </patternFill>
     </fill>
   </fills>
@@ -71,7 +77,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -80,6 +86,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -447,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -459,7 +468,7 @@
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="19" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="25" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
@@ -523,7 +532,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>02-MAR-26</t>
+          <t>24-MAY-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -533,26 +542,26 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-676</t>
+          <t>flyadeal F3-775</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>672</v>
+        <v>489</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>758</v>
+        <v>954</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-86</v>
+        <v>-465</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>-16</v>
+        <v>15</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
@@ -568,7 +577,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>02-MAR-26</t>
+          <t>24-MAY-26</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -578,26 +587,26 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-694</t>
+          <t>flyadeal F3-771</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>672</v>
+        <v>489</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>758</v>
+        <v>954</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-86</v>
+        <v>-465</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>-16</v>
+        <v>15</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
@@ -613,7 +622,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>02-MAR-26</t>
+          <t>31-MAY-26</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -623,30 +632,30 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-696</t>
+          <t>flyadeal F3-775</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>680</v>
+        <v>699</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>758</v>
+        <v>1338</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-78</v>
+        <v>-639</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+        <v>15</v>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -658,7 +667,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>02-MAR-26</t>
+          <t>31-MAY-26</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -668,26 +677,26 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-678</t>
+          <t>flynas XY-576</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>728</v>
+        <v>799</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>758</v>
+        <v>1338</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-30</v>
+        <v>-539</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>-16</v>
+        <v>10</v>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
@@ -703,7 +712,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>02-MAR-26</t>
+          <t>31-MAY-26</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -713,26 +722,26 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-640</t>
+          <t>flyadeal F3-771</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>738</v>
+        <v>1099</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>758</v>
+        <v>1338</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-20</v>
+        <v>-239</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>-16</v>
+        <v>-10</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
@@ -748,7 +757,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>03-MAR-26</t>
+          <t>07-JUN-26</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -758,26 +767,26 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-676</t>
+          <t>flynas XY-576</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>558</v>
+        <v>429</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>620</v>
+        <v>798</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-62</v>
+        <v>-369</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>-16</v>
+        <v>10</v>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
@@ -793,7 +802,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>03-MAR-26</t>
+          <t>14-JUN-26</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -803,26 +812,26 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-694</t>
+          <t>flynas XY-576</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>558</v>
+        <v>399</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>620</v>
+        <v>798</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-62</v>
+        <v>-399</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="H8" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>-16</v>
+        <v>10</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
@@ -838,7 +847,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>07-MAR-26</t>
+          <t>21-JUN-26</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -848,26 +857,26 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-676</t>
+          <t>flynas XY-576</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>558</v>
+        <v>659</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>560</v>
+        <v>798</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-2</v>
+        <v>-139</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H9" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>-16</v>
+        <v>-10</v>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
@@ -875,96 +884,6 @@
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>07-MAR-26</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>SM-488</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-694</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="n">
-        <v>558</v>
-      </c>
-      <c r="E10" s="2" t="n">
-        <v>560</v>
-      </c>
-      <c r="F10" s="2" t="n">
-        <v>-2</v>
-      </c>
-      <c r="G10" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H10" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I10" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>07-MAR-26</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>SM-488</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-678</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="n">
-        <v>560</v>
-      </c>
-      <c r="E11" s="2" t="n">
-        <v>560</v>
-      </c>
-      <c r="F11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H11" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I11" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>SAR</t>
         </is>

--- a/excel_routes/route_MED_ATZ_threats.xlsx
+++ b/excel_routes/route_MED_ATZ_threats.xlsx
@@ -54,8 +54,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF3CD"/>
-        <bgColor rgb="00FFF3CD"/>
+        <fgColor rgb="00F8D7DA"/>
+        <bgColor rgb="00F8D7DA"/>
       </patternFill>
     </fill>
   </fills>
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:K17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -468,7 +468,7 @@
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="19" customWidth="1" min="9" max="9"/>
-    <col width="25" customWidth="1" min="10" max="10"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
@@ -546,13 +546,13 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>489</v>
+        <v>899</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>954</v>
+        <v>1360</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-465</v>
+        <v>-461</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>15</v>
@@ -587,30 +587,30 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-771</t>
+          <t>EgyptAir MS-696</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>489</v>
+        <v>923</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>954</v>
+        <v>1360</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-465</v>
+        <v>-437</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+        <v>-16</v>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -622,7 +622,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>31-MAY-26</t>
+          <t>24-MAY-26</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -632,30 +632,30 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-775</t>
+          <t>EgyptAir MS-676</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>895</v>
+        <v>931</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>1338</v>
+        <v>1360</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-443</v>
+        <v>-429</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -667,7 +667,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>31-MAY-26</t>
+          <t>24-MAY-26</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -677,30 +677,30 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-576</t>
+          <t>EgyptAir MS-678</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>989</v>
+        <v>980</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>1338</v>
+        <v>1360</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-349</v>
+        <v>-380</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>-10</v>
+        <v>-16</v>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -712,7 +712,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>31-MAY-26</t>
+          <t>24-MAY-26</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -722,26 +722,26 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-771</t>
+          <t>flynas XY-793</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>1099</v>
+        <v>1009</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>1338</v>
+        <v>1360</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-239</v>
+        <v>-351</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
@@ -757,7 +757,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>07-JUN-26</t>
+          <t>24-MAY-26</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -771,22 +771,22 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>429</v>
+        <v>1009</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>798</v>
+        <v>1360</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-369</v>
+        <v>-351</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>14-JUN-26</t>
+          <t>05-JUL-26</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -812,26 +812,26 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-576</t>
+          <t>EgyptAir MS-676</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>589</v>
+        <v>833</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>798</v>
+        <v>976</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-209</v>
+        <v>-143</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H8" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>-10</v>
+        <v>-16</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
@@ -847,7 +847,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>14-JUN-26</t>
+          <t>05-JUL-26</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -857,17 +857,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-391</t>
+          <t>EgyptAir MS-694</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>698</v>
+        <v>833</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>798</v>
+        <v>976</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-100</v>
+        <v>-143</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>46</v>
@@ -892,7 +892,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>21-JUN-26</t>
+          <t>05-JUL-26</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -902,33 +902,348 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>EgyptAir MS-696</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>833</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>976</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>-143</v>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I10" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>05-JUL-26</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>SM-488</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-640</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>833</v>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>976</v>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>-143</v>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H11" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I11" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>12-JUL-26</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>SM-488</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-775</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>799</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>976</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>-177</v>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="H12" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I12" s="2" t="n">
+        <v>-10</v>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>12-JUL-26</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>SM-488</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-771</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>826</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>976</v>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>-150</v>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="H13" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I13" s="2" t="n">
+        <v>-10</v>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>12-JUL-26</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>SM-488</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-694</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>833</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>976</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>-143</v>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H14" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I14" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>12-JUL-26</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>SM-488</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-381</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>903</v>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>976</v>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>-73</v>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H15" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I15" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>12-JUL-26</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>SM-488</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-319</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>903</v>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>976</v>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>-73</v>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H16" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I16" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>12-JUL-26</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>SM-488</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
           <t>flynas XY-576</t>
         </is>
       </c>
-      <c r="D10" s="2" t="n">
-        <v>659</v>
-      </c>
-      <c r="E10" s="2" t="n">
-        <v>798</v>
-      </c>
-      <c r="F10" s="2" t="n">
-        <v>-139</v>
-      </c>
-      <c r="G10" s="2" t="n">
+      <c r="D17" s="2" t="n">
+        <v>906</v>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>976</v>
+      </c>
+      <c r="F17" s="2" t="n">
+        <v>-70</v>
+      </c>
+      <c r="G17" s="2" t="n">
         <v>40</v>
       </c>
-      <c r="H10" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I10" s="2" t="n">
+      <c r="H17" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I17" s="2" t="n">
         <v>-10</v>
       </c>
-      <c r="J10" s="3" t="inlineStr">
+      <c r="J17" s="3" t="inlineStr">
         <is>
           <t>LOW THREAT</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>SAR</t>
         </is>

--- a/excel_routes/route_MED_ATZ_threats.xlsx
+++ b/excel_routes/route_MED_ATZ_threats.xlsx
@@ -468,7 +468,7 @@
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="19" customWidth="1" min="9" max="9"/>
-    <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
@@ -565,7 +565,7 @@
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="J3" s="4" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -655,7 +655,7 @@
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -700,7 +700,7 @@
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -745,7 +745,7 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -790,7 +790,7 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -835,7 +835,7 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -925,7 +925,7 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -970,7 +970,7 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1015,7 +1015,7 @@
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1060,7 +1060,7 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1240,7 +1240,7 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">

--- a/excel_routes/route_MED_ATZ_threats.xlsx
+++ b/excel_routes/route_MED_ATZ_threats.xlsx
@@ -33,7 +33,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -48,14 +48,20 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D4EDDA"/>
-        <bgColor rgb="00D4EDDA"/>
+        <fgColor rgb="00F8D7DA"/>
+        <bgColor rgb="00F8D7DA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F8D7DA"/>
-        <bgColor rgb="00F8D7DA"/>
+        <fgColor rgb="00FFF3CD"/>
+        <bgColor rgb="00FFF3CD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D4EDDA"/>
+        <bgColor rgb="00D4EDDA"/>
       </patternFill>
     </fill>
   </fills>
@@ -77,7 +83,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -89,6 +95,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -456,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K17"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -542,30 +551,30 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-775</t>
+          <t>EgyptAir MS-696</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>899</v>
+        <v>753</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>1360</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-461</v>
+        <v>-607</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>15</v>
+        <v>-16</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -587,17 +596,17 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-696</t>
+          <t>EgyptAir MS-676</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>923</v>
+        <v>761</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>1360</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-437</v>
+        <v>-599</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>46</v>
@@ -608,7 +617,7 @@
       <c r="I3" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J3" s="4" t="inlineStr">
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -632,17 +641,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-676</t>
+          <t>EgyptAir MS-678</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>931</v>
+        <v>810</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>1360</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-429</v>
+        <v>-550</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>46</v>
@@ -653,7 +662,7 @@
       <c r="I4" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J4" s="4" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -677,30 +686,30 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-678</t>
+          <t>flynas XY-793</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>980</v>
+        <v>1026</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>1360</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-380</v>
+        <v>-334</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>-16</v>
+        <v>-10</v>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -722,30 +731,30 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-793</t>
+          <t>flynas XY-576</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>1009</v>
+        <v>1026</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>1360</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-351</v>
+        <v>-334</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-10</v>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -767,17 +776,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-576</t>
+          <t>flyadeal F3-775</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>1009</v>
+        <v>1076</v>
       </c>
       <c r="E7" s="2" t="n">
         <v>1360</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-351</v>
+        <v>-284</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>30</v>
@@ -788,7 +797,7 @@
       <c r="I7" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J7" s="3" t="inlineStr">
+      <c r="J7" s="5" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -812,17 +821,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-676</t>
+          <t>EgyptAir MS-678</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>833</v>
+        <v>810</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-143</v>
+        <v>-166</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>46</v>
@@ -833,9 +842,9 @@
       <c r="I8" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -857,7 +866,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-694</t>
+          <t>EgyptAir MS-676</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
@@ -878,7 +887,7 @@
       <c r="I9" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J9" s="3" t="inlineStr">
+      <c r="J9" s="5" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -902,7 +911,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-696</t>
+          <t>EgyptAir MS-694</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
@@ -923,7 +932,7 @@
       <c r="I10" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J10" s="3" t="inlineStr">
+      <c r="J10" s="5" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -947,7 +956,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-640</t>
+          <t>EgyptAir MS-696</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
@@ -968,7 +977,7 @@
       <c r="I11" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J11" s="3" t="inlineStr">
+      <c r="J11" s="5" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -982,7 +991,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>12-JUL-26</t>
+          <t>05-JUL-26</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -992,28 +1001,28 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-775</t>
+          <t>EgyptAir MS-640</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>799</v>
+        <v>833</v>
       </c>
       <c r="E12" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-177</v>
+        <v>-143</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H12" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J12" s="3" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="J12" s="5" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -1037,28 +1046,28 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-771</t>
+          <t>EgyptAir MS-694</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>826</v>
+        <v>833</v>
       </c>
       <c r="E13" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-150</v>
+        <v>-143</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H13" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J13" s="3" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="J13" s="5" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -1082,17 +1091,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-694</t>
+          <t>Saudia SV-381</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>833</v>
+        <v>903</v>
       </c>
       <c r="E14" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-143</v>
+        <v>-73</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>46</v>
@@ -1103,147 +1112,12 @@
       <c r="I14" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J14" s="3" t="inlineStr">
+      <c r="J14" s="5" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>12-JUL-26</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>SM-488</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>Saudia SV-381</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="n">
-        <v>903</v>
-      </c>
-      <c r="E15" s="2" t="n">
-        <v>976</v>
-      </c>
-      <c r="F15" s="2" t="n">
-        <v>-73</v>
-      </c>
-      <c r="G15" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H15" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I15" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>12-JUL-26</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>SM-488</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>Saudia SV-319</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="n">
-        <v>903</v>
-      </c>
-      <c r="E16" s="2" t="n">
-        <v>976</v>
-      </c>
-      <c r="F16" s="2" t="n">
-        <v>-73</v>
-      </c>
-      <c r="G16" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H16" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I16" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>12-JUL-26</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>SM-488</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>flynas XY-576</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="n">
-        <v>906</v>
-      </c>
-      <c r="E17" s="2" t="n">
-        <v>976</v>
-      </c>
-      <c r="F17" s="2" t="n">
-        <v>-70</v>
-      </c>
-      <c r="G17" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="H17" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I17" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>SAR</t>
         </is>

--- a/excel_routes/route_MED_ATZ_threats.xlsx
+++ b/excel_routes/route_MED_ATZ_threats.xlsx
@@ -54,14 +54,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF3CD"/>
-        <bgColor rgb="00FFF3CD"/>
+        <fgColor rgb="00D4EDDA"/>
+        <bgColor rgb="00D4EDDA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D4EDDA"/>
-        <bgColor rgb="00D4EDDA"/>
+        <fgColor rgb="00FFF3CD"/>
+        <bgColor rgb="00FFF3CD"/>
       </patternFill>
     </fill>
   </fills>
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:K13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -551,17 +551,17 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-696</t>
+          <t>EgyptAir MS-676</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>753</v>
+        <v>761</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>1360</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-607</v>
+        <v>-599</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>46</v>
@@ -596,30 +596,30 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-676</t>
+          <t>flyadeal F3-775</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>761</v>
+        <v>799</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>1360</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-599</v>
+        <v>-561</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>15</v>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -686,30 +686,30 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-793</t>
+          <t>EgyptAir MS-696</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>1026</v>
+        <v>833</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>1360</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-334</v>
+        <v>-527</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J5" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>-16</v>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -731,28 +731,28 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-576</t>
+          <t>flynas XY-793</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>1026</v>
+        <v>909</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>1360</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-334</v>
+        <v>-451</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J6" s="4" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J6" s="5" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -776,17 +776,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-775</t>
+          <t>flynas XY-576</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>1076</v>
+        <v>909</v>
       </c>
       <c r="E7" s="2" t="n">
         <v>1360</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-284</v>
+        <v>-451</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>30</v>
@@ -799,7 +799,7 @@
       </c>
       <c r="J7" s="5" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -821,17 +821,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-678</t>
+          <t>EgyptAir MS-676</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>810</v>
+        <v>833</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-166</v>
+        <v>-143</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>46</v>
@@ -844,7 +844,7 @@
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-676</t>
+          <t>EgyptAir MS-694</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
@@ -887,7 +887,7 @@
       <c r="I9" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J9" s="5" t="inlineStr">
+      <c r="J9" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -911,7 +911,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-694</t>
+          <t>EgyptAir MS-696</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
@@ -932,7 +932,7 @@
       <c r="I10" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J10" s="5" t="inlineStr">
+      <c r="J10" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -956,7 +956,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-696</t>
+          <t>EgyptAir MS-640</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
@@ -977,7 +977,7 @@
       <c r="I11" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J11" s="5" t="inlineStr">
+      <c r="J11" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -991,7 +991,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>05-JUL-26</t>
+          <t>12-JUL-26</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -1005,13 +1005,13 @@
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>833</v>
+        <v>753</v>
       </c>
       <c r="E12" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-143</v>
+        <v>-223</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>46</v>
@@ -1024,7 +1024,7 @@
       </c>
       <c r="J12" s="5" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1067,57 +1067,12 @@
       <c r="I13" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J13" s="5" t="inlineStr">
+      <c r="J13" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>12-JUL-26</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>SM-488</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>Saudia SV-381</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="n">
-        <v>903</v>
-      </c>
-      <c r="E14" s="2" t="n">
-        <v>976</v>
-      </c>
-      <c r="F14" s="2" t="n">
-        <v>-73</v>
-      </c>
-      <c r="G14" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H14" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I14" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J14" s="5" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>SAR</t>
         </is>

--- a/excel_routes/route_MED_ATZ_threats.xlsx
+++ b/excel_routes/route_MED_ATZ_threats.xlsx
@@ -54,14 +54,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D4EDDA"/>
-        <bgColor rgb="00D4EDDA"/>
+        <fgColor rgb="00FFF3CD"/>
+        <bgColor rgb="00FFF3CD"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF3CD"/>
-        <bgColor rgb="00FFF3CD"/>
+        <fgColor rgb="00D4EDDA"/>
+        <bgColor rgb="00D4EDDA"/>
       </patternFill>
     </fill>
   </fills>
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K13"/>
+  <dimension ref="A1:K24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -477,7 +477,7 @@
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="19" customWidth="1" min="9" max="9"/>
-    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
@@ -541,27 +541,27 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>24-MAY-26</t>
+          <t>21-MAY-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>SM-488</t>
+          <t>SM-436</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-676</t>
+          <t>EgyptAir MS-696</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>761</v>
+        <v>753</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1360</v>
+        <v>1753</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-599</v>
+        <v>-1000</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>46</v>
@@ -574,7 +574,7 @@
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -586,40 +586,40 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>24-MAY-26</t>
+          <t>21-MAY-26</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>SM-488</t>
+          <t>SM-436</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-775</t>
+          <t>EgyptAir MS-640</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>799</v>
+        <v>753</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>1360</v>
+        <v>1753</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-561</v>
+        <v>-1000</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J3" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -631,27 +631,27 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>24-MAY-26</t>
+          <t>21-MAY-26</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>SM-488</t>
+          <t>SM-436</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-678</t>
+          <t>EgyptAir MS-680</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>810</v>
+        <v>753</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>1360</v>
+        <v>1753</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-550</v>
+        <v>-1000</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>46</v>
@@ -664,7 +664,7 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -676,40 +676,40 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>24-MAY-26</t>
+          <t>21-MAY-26</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>SM-488</t>
+          <t>SM-436</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-696</t>
+          <t>flyadeal F3-771</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>833</v>
+        <v>796</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>1360</v>
+        <v>1753</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-527</v>
+        <v>-957</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -721,40 +721,40 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>24-MAY-26</t>
+          <t>21-MAY-26</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>SM-488</t>
+          <t>SM-436</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-793</t>
+          <t>EgyptAir MS-678</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>909</v>
+        <v>890</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>1360</v>
+        <v>1753</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-451</v>
+        <v>-863</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" s="5" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>-16</v>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>24-MAY-26</t>
+          <t>21-MAY-26</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>SM-488</t>
+          <t>SM-436</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -783,10 +783,10 @@
         <v>909</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>1360</v>
+        <v>1753</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-451</v>
+        <v>-844</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>30</v>
@@ -797,9 +797,9 @@
       <c r="I7" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J7" s="5" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -811,40 +811,40 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>05-JUL-26</t>
+          <t>21-MAY-26</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>SM-488</t>
+          <t>SM-436</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-676</t>
+          <t>flynas XY-793</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>833</v>
+        <v>926</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>976</v>
+        <v>1753</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-143</v>
+        <v>-827</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H8" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J8" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-10</v>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -856,27 +856,27 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>05-JUL-26</t>
+          <t>21-MAY-26</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>SM-488</t>
+          <t>SM-436</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-694</t>
+          <t>EgyptAir MS-676</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>833</v>
+        <v>1018</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>976</v>
+        <v>1753</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-143</v>
+        <v>-735</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>46</v>
@@ -887,9 +887,9 @@
       <c r="I9" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J9" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -901,27 +901,27 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>05-JUL-26</t>
+          <t>21-MAY-26</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>SM-488</t>
+          <t>SM-436</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-696</t>
+          <t>EgyptAir MS-694</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>833</v>
+        <v>1018</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>976</v>
+        <v>1753</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-143</v>
+        <v>-735</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>46</v>
@@ -932,9 +932,9 @@
       <c r="I10" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J10" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -946,40 +946,40 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>05-JUL-26</t>
+          <t>21-MAY-26</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>SM-488</t>
+          <t>SM-436</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-640</t>
+          <t>Saudia SV-391</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>833</v>
+        <v>1076</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>976</v>
+        <v>1753</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-143</v>
+        <v>-677</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H11" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>-16</v>
+        <v>7</v>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -991,40 +991,40 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>12-JUL-26</t>
+          <t>21-MAY-26</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>SM-488</t>
+          <t>SM-436</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-640</t>
+          <t>Saudia SV-317</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>753</v>
+        <v>1076</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>976</v>
+        <v>1753</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-223</v>
+        <v>-677</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H12" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J12" s="5" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>7</v>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1036,43 +1036,538 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>24-MAY-26</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>SM-488</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-775</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>699</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>1246</v>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>-547</v>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H13" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I13" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J13" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>24-MAY-26</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>SM-488</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-576</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>739</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>1246</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>-507</v>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H14" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>24-MAY-26</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>SM-488</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-793</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>809</v>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>1246</v>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>-437</v>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H15" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>24-MAY-26</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>SM-488</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-678</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>810</v>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>1246</v>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>-436</v>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H16" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I16" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>24-MAY-26</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>SM-488</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-676</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>841</v>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>1246</v>
+      </c>
+      <c r="F17" s="2" t="n">
+        <v>-405</v>
+      </c>
+      <c r="G17" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H17" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I17" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>24-MAY-26</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>SM-488</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-696</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>1018</v>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>1246</v>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>-228</v>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H18" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I18" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>05-JUL-26</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>SM-488</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-676</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="n">
+        <v>833</v>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>976</v>
+      </c>
+      <c r="F19" s="2" t="n">
+        <v>-143</v>
+      </c>
+      <c r="G19" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H19" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I19" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J19" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>05-JUL-26</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>SM-488</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-694</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>833</v>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>976</v>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>-143</v>
+      </c>
+      <c r="G20" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H20" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I20" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J20" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>05-JUL-26</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>SM-488</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-696</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>833</v>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>976</v>
+      </c>
+      <c r="F21" s="2" t="n">
+        <v>-143</v>
+      </c>
+      <c r="G21" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H21" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I21" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J21" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>05-JUL-26</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>SM-488</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-640</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>833</v>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>976</v>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>-143</v>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H22" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I22" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J22" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
           <t>12-JUL-26</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>SM-488</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-640</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="n">
+        <v>753</v>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>976</v>
+      </c>
+      <c r="F23" s="2" t="n">
+        <v>-223</v>
+      </c>
+      <c r="G23" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H23" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I23" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>12-JUL-26</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>SM-488</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
         <is>
           <t>EgyptAir MS-694</t>
         </is>
       </c>
-      <c r="D13" s="2" t="n">
+      <c r="D24" s="2" t="n">
         <v>833</v>
       </c>
-      <c r="E13" s="2" t="n">
+      <c r="E24" s="2" t="n">
         <v>976</v>
       </c>
-      <c r="F13" s="2" t="n">
+      <c r="F24" s="2" t="n">
         <v>-143</v>
       </c>
-      <c r="G13" s="2" t="n">
+      <c r="G24" s="2" t="n">
         <v>46</v>
       </c>
-      <c r="H13" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I13" s="2" t="n">
+      <c r="H24" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I24" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J13" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="J24" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>SAR</t>
         </is>

--- a/excel_routes/route_MED_ATZ_threats.xlsx
+++ b/excel_routes/route_MED_ATZ_threats.xlsx
@@ -523,24 +523,24 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>21-JUN-26</t>
+          <t>23-JUN-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>SM-252</t>
+          <t>SM-254</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-101</t>
+          <t>EgyptAir MS-103</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>1550</v>
+        <v>1650</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1730</v>
+        <v>1790</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>-200</v>

--- a/excel_routes/route_MED_ATZ_threats.xlsx
+++ b/excel_routes/route_MED_ATZ_threats.xlsx
@@ -48,8 +48,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F8D7DA"/>
-        <bgColor rgb="00F8D7DA"/>
+        <fgColor rgb="00FFF3CD"/>
+        <bgColor rgb="00FFF3CD"/>
       </patternFill>
     </fill>
   </fills>
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -459,7 +459,7 @@
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="19" customWidth="1" min="9" max="9"/>
-    <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
@@ -523,43 +523,133 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>23-JUN-26</t>
+          <t>24-MAY-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>SM-254</t>
+          <t>SM-488</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-103</t>
+          <t>flynas XY-793</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>1650</v>
+        <v>809</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1790</v>
+        <v>1246</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-200</v>
+        <v>-437</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>30</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>24-MAY-26</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>SM-488</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-576</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>809</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>1246</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>-437</v>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>24-MAY-26</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>SM-488</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-696</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>1018</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>1246</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>-228</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I4" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>SAR</t>
         </is>

--- a/excel_routes/route_MED_ATZ_threats.xlsx
+++ b/excel_routes/route_MED_ATZ_threats.xlsx
@@ -533,26 +533,26 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-793</t>
+          <t>flynas XY-576</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>809</v>
+        <v>709</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1246</v>
+        <v>1360</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-437</v>
+        <v>-651</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
@@ -578,26 +578,26 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-576</t>
+          <t>EgyptAir MS-676</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>809</v>
+        <v>1026</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>1246</v>
+        <v>1360</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-437</v>
+        <v>-334</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
@@ -623,17 +623,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-696</t>
+          <t>EgyptAir MS-678</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>1018</v>
+        <v>1075</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>1246</v>
+        <v>1360</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-228</v>
+        <v>-285</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>46</v>

--- a/excel_routes/route_MED_ATZ_threats.xlsx
+++ b/excel_routes/route_MED_ATZ_threats.xlsx
@@ -48,8 +48,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF3CD"/>
-        <bgColor rgb="00FFF3CD"/>
+        <fgColor rgb="00D4EDDA"/>
+        <bgColor rgb="00D4EDDA"/>
       </patternFill>
     </fill>
   </fills>
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -533,17 +533,17 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-576</t>
+          <t>flyadeal F3-775</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>709</v>
+        <v>719</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1360</v>
+        <v>1246</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-651</v>
+        <v>-527</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>15</v>
@@ -556,7 +556,7 @@
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -578,30 +578,30 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-676</t>
+          <t>flynas XY-793</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>1026</v>
+        <v>809</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>1360</v>
+        <v>1246</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-334</v>
+        <v>-437</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>-16</v>
+        <v>15</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -623,33 +623,168 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-678</t>
+          <t>flynas XY-576</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>1075</v>
+        <v>809</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>1360</v>
+        <v>1246</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-285</v>
+        <v>-437</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I4" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>05-JUL-26</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>SM-488</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-771</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>469</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>976</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>-507</v>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I5" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>05-JUL-26</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>SM-488</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-576</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>499</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>976</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>-477</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>12-JUL-26</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>SM-488</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-694</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>833</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>976</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>-143</v>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I7" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>SAR</t>
         </is>

--- a/excel_routes/route_MED_ATZ_threats.xlsx
+++ b/excel_routes/route_MED_ATZ_threats.xlsx
@@ -33,7 +33,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -44,6 +44,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="003498DB"/>
         <bgColor rgb="003498DB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF3CD"/>
+        <bgColor rgb="00FFF3CD"/>
       </patternFill>
     </fill>
     <fill>
@@ -71,7 +77,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -80,6 +86,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -447,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -533,30 +542,30 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-775</t>
+          <t>EgyptAir MS-676</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>719</v>
+        <v>1026</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1246</v>
+        <v>1360</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-527</v>
+        <v>-334</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>15</v>
+        <v>-16</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -578,30 +587,30 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-793</t>
+          <t>EgyptAir MS-678</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>809</v>
+        <v>1075</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>1246</v>
+        <v>1360</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-437</v>
+        <v>-285</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>15</v>
+        <v>-16</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -623,28 +632,28 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-576</t>
+          <t>EgyptAir MS-696</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>809</v>
+        <v>1223</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>1246</v>
+        <v>1360</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-437</v>
+        <v>-137</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -689,7 +698,7 @@
       <c r="I5" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="J5" s="3" t="inlineStr">
+      <c r="J5" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -734,7 +743,7 @@
       <c r="I6" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="J6" s="3" t="inlineStr">
+      <c r="J6" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -758,33 +767,123 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-694</t>
+          <t>flyadeal F3-775</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>833</v>
+        <v>439</v>
       </c>
       <c r="E7" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-143</v>
+        <v>-537</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I7" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>12-JUL-26</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>SM-488</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-771</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>469</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>976</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>-507</v>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>12-JUL-26</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>SM-488</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-694</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>833</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>976</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>-143</v>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H9" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I9" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J7" s="3" t="inlineStr">
+      <c r="J9" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>SAR</t>
         </is>

--- a/excel_routes/route_MED_ATZ_threats.xlsx
+++ b/excel_routes/route_MED_ATZ_threats.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -542,26 +542,26 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-676</t>
+          <t>flynas XY-793</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>1026</v>
+        <v>999</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>1360</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-334</v>
+        <v>-361</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>-16</v>
+        <v>-10</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
@@ -587,17 +587,17 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-678</t>
+          <t>EgyptAir MS-676</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>1075</v>
+        <v>1026</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>1360</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-285</v>
+        <v>-334</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>46</v>
@@ -632,17 +632,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-696</t>
+          <t>EgyptAir MS-678</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>1223</v>
+        <v>1075</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>1360</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-137</v>
+        <v>-285</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>46</v>
@@ -653,9 +653,9 @@
       <c r="I4" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J4" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -757,7 +757,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>12-JUL-26</t>
+          <t>05-JUL-26</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -771,22 +771,22 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>439</v>
+        <v>819</v>
       </c>
       <c r="E7" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-537</v>
+        <v>-157</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>15</v>
+        <v>-10</v>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
@@ -812,17 +812,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-771</t>
+          <t>flyadeal F3-775</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>469</v>
+        <v>439</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-507</v>
+        <v>-537</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>15</v>
@@ -857,33 +857,78 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-694</t>
+          <t>flynas XY-576</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>833</v>
+        <v>689</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-143</v>
+        <v>-287</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H9" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I9" s="2" t="n">
+        <v>-10</v>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>12-JUL-26</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>SM-488</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-694</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>833</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>976</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>-143</v>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I10" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J9" s="4" t="inlineStr">
+      <c r="J10" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>SAR</t>
         </is>

--- a/excel_routes/route_MED_ATZ_threats.xlsx
+++ b/excel_routes/route_MED_ATZ_threats.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -542,26 +542,26 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-793</t>
+          <t>EgyptAir MS-678</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>999</v>
+        <v>1075</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>1360</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-361</v>
+        <v>-285</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>-10</v>
+        <v>-16</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
@@ -587,17 +587,17 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-676</t>
+          <t>EgyptAir MS-696</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>1026</v>
+        <v>1223</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>1360</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-334</v>
+        <v>-137</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>46</v>
@@ -608,9 +608,9 @@
       <c r="I3" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -632,17 +632,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-678</t>
+          <t>EgyptAir MS-676</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>1075</v>
+        <v>1231</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>1360</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-285</v>
+        <v>-129</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>46</v>
@@ -653,9 +653,9 @@
       <c r="I4" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -757,7 +757,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>05-JUL-26</t>
+          <t>12-JUL-26</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -767,26 +767,26 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-775</t>
+          <t>EgyptAir MS-694</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>819</v>
+        <v>833</v>
       </c>
       <c r="E7" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-157</v>
+        <v>-143</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>-10</v>
+        <v>-16</v>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
@@ -794,141 +794,6 @@
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>12-JUL-26</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>SM-488</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>flyadeal F3-775</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="n">
-        <v>439</v>
-      </c>
-      <c r="E8" s="2" t="n">
-        <v>976</v>
-      </c>
-      <c r="F8" s="2" t="n">
-        <v>-537</v>
-      </c>
-      <c r="G8" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="H8" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I8" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J8" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>12-JUL-26</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>SM-488</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>flynas XY-576</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="n">
-        <v>689</v>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>976</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>-287</v>
-      </c>
-      <c r="G9" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="H9" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I9" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>12-JUL-26</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>SM-488</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-694</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="n">
-        <v>833</v>
-      </c>
-      <c r="E10" s="2" t="n">
-        <v>976</v>
-      </c>
-      <c r="F10" s="2" t="n">
-        <v>-143</v>
-      </c>
-      <c r="G10" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H10" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I10" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J10" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>SAR</t>
         </is>

--- a/excel_routes/route_MED_ATZ_threats.xlsx
+++ b/excel_routes/route_MED_ATZ_threats.xlsx
@@ -33,7 +33,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -44,12 +44,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="003498DB"/>
         <bgColor rgb="003498DB"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF3CD"/>
-        <bgColor rgb="00FFF3CD"/>
       </patternFill>
     </fill>
     <fill>
@@ -77,7 +71,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -86,9 +80,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -532,7 +523,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>24-MAY-26</t>
+          <t>05-JUL-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -542,30 +533,30 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-678</t>
+          <t>flyadeal F3-775</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>1075</v>
+        <v>469</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1360</v>
+        <v>976</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-285</v>
+        <v>-507</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>-16</v>
+        <v>15</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -577,7 +568,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>24-MAY-26</t>
+          <t>05-JUL-26</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -587,28 +578,28 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-696</t>
+          <t>flynas XY-576</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>1223</v>
+        <v>499</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>1360</v>
+        <v>976</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-137</v>
+        <v>-477</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J3" s="4" t="inlineStr">
+        <v>15</v>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -622,7 +613,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>24-MAY-26</t>
+          <t>05-JUL-26</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -632,28 +623,28 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-676</t>
+          <t>flyadeal F3-771</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>1231</v>
+        <v>509</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>1360</v>
+        <v>976</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-129</v>
+        <v>-467</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J4" s="4" t="inlineStr">
+        <v>15</v>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -667,7 +658,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>05-JUL-26</t>
+          <t>12-JUL-26</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -677,17 +668,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-771</t>
+          <t>flyadeal F3-775</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>469</v>
+        <v>439</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-507</v>
+        <v>-537</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>15</v>
@@ -698,7 +689,7 @@
       <c r="I5" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="J5" s="4" t="inlineStr">
+      <c r="J5" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -712,7 +703,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>05-JUL-26</t>
+          <t>12-JUL-26</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -722,17 +713,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-576</t>
+          <t>flyadeal F3-771</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>499</v>
+        <v>469</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-477</v>
+        <v>-507</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>15</v>
@@ -743,7 +734,7 @@
       <c r="I6" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="J6" s="4" t="inlineStr">
+      <c r="J6" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -771,13 +762,13 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>833</v>
+        <v>870</v>
       </c>
       <c r="E7" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-143</v>
+        <v>-106</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>46</v>
@@ -788,7 +779,7 @@
       <c r="I7" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J7" s="4" t="inlineStr">
+      <c r="J7" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>

--- a/excel_routes/route_MED_ATZ_threats.xlsx
+++ b/excel_routes/route_MED_ATZ_threats.xlsx
@@ -33,7 +33,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -50,6 +50,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00D4EDDA"/>
         <bgColor rgb="00D4EDDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF3CD"/>
+        <bgColor rgb="00FFF3CD"/>
       </patternFill>
     </fill>
   </fills>
@@ -71,7 +77,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -80,6 +86,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -447,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -533,17 +542,17 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-775</t>
+          <t>flynas XY-576</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>469</v>
+        <v>434</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-507</v>
+        <v>-542</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>15</v>
@@ -578,26 +587,26 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-576</t>
+          <t>EgyptAir MS-676</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>499</v>
+        <v>620</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-477</v>
+        <v>-356</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
@@ -623,26 +632,26 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-771</t>
+          <t>EgyptAir MS-694</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>509</v>
+        <v>620</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-467</v>
+        <v>-356</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
@@ -668,17 +677,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-775</t>
+          <t>flynas XY-576</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-537</v>
+        <v>-542</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>15</v>
@@ -713,17 +722,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-771</t>
+          <t>flyadeal F3-775</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>469</v>
+        <v>439</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-507</v>
+        <v>-537</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>15</v>
@@ -762,13 +771,13 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>870</v>
+        <v>701</v>
       </c>
       <c r="E7" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-106</v>
+        <v>-275</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>46</v>
@@ -779,12 +788,102 @@
       <c r="I7" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J7" s="3" t="inlineStr">
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>26-JUL-26</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>SM-488</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-676</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>653</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>622</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>26-JUL-26</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>SM-488</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-640</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>653</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>622</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H9" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I9" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>SAR</t>
         </is>
